--- a/backend/data/financials_by_company/0607.HK.xlsx
+++ b/backend/data/financials_by_company/0607.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,617 +677,672 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1881926750</v>
+        <v>-453535500</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>2334844000</v>
+        <v>829200000</v>
       </c>
       <c r="E2" t="n">
-        <v>-7527707000</v>
+        <v>-1814142000</v>
       </c>
       <c r="F2" t="n">
-        <v>-7527707000</v>
+        <v>-1814142000</v>
       </c>
       <c r="G2" t="n">
-        <v>-6013900000</v>
+        <v>-2717093000</v>
       </c>
       <c r="H2" t="n">
-        <v>947865000</v>
+        <v>658041000</v>
       </c>
       <c r="I2" t="n">
-        <v>19654507000</v>
+        <v>17490747000</v>
       </c>
       <c r="J2" t="n">
-        <v>-5192863000</v>
+        <v>-984942000</v>
       </c>
       <c r="K2" t="n">
-        <v>-6140728000</v>
+        <v>-1642983000</v>
       </c>
       <c r="L2" t="n">
-        <v>-863092000</v>
+        <v>-249358000</v>
       </c>
       <c r="M2" t="n">
-        <v>997693000</v>
+        <v>452375000</v>
       </c>
       <c r="N2" t="n">
-        <v>134601000</v>
+        <v>203017000</v>
       </c>
       <c r="O2" t="n">
-        <v>-368119750</v>
+        <v>-1356486500</v>
       </c>
       <c r="P2" t="n">
-        <v>-6013900000</v>
+        <v>-2685344000</v>
       </c>
       <c r="Q2" t="n">
-        <v>21617082000</v>
+        <v>19369414000</v>
       </c>
       <c r="R2" t="n">
-        <v>-6073537000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>636763934</v>
-      </c>
-      <c r="T2" t="n">
-        <v>636763934</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-9.444000000000001</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-9.444000000000001</v>
-      </c>
+        <v>-249004000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-6013900000</v>
+        <v>-2685344000</v>
       </c>
       <c r="X2" t="n">
-        <v>-6013900000</v>
+        <v>-2685344000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-6013900000</v>
+        <v>-2685344000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1311450000</v>
+        <v>-349586000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-7325350000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>-2335758000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>31749000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-7325350000</v>
+        <v>-2367507000</v>
       </c>
       <c r="AE2" t="n">
-        <v>186929000</v>
+        <v>272149000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-7138421000</v>
+        <v>-2095358000</v>
       </c>
       <c r="AG2" t="n">
-        <v>65210000</v>
+        <v>60698000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-7428884000</v>
+        <v>30528000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-7155000</v>
+        <v>-206201000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7198175000</v>
+        <v>93588000</v>
       </c>
       <c r="AK2" t="n">
-        <v>237864000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>82232000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-147000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-863092000</v>
+        <v>-249358000</v>
       </c>
       <c r="AN2" t="n">
-        <v>997693000</v>
+        <v>452375000</v>
       </c>
       <c r="AO2" t="n">
-        <v>134601000</v>
+        <v>203017000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1530834000</v>
+        <v>1416128000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1962575000</v>
+        <v>1878667000</v>
       </c>
       <c r="AR2" t="n">
-        <v>809474000</v>
+        <v>667782000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1446076000</v>
+        <v>1344498000</v>
       </c>
       <c r="AT2" t="n">
-        <v>619837000</v>
+        <v>512769000</v>
       </c>
       <c r="AU2" t="n">
-        <v>826239000</v>
+        <v>831729000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3493409000</v>
+        <v>3294795000</v>
       </c>
       <c r="AW2" t="n">
-        <v>19654507000</v>
+        <v>17490747000</v>
       </c>
       <c r="AX2" t="n">
-        <v>23147916000</v>
+        <v>20785542000</v>
       </c>
       <c r="AY2" t="n">
-        <v>23147916000</v>
+        <v>20785542000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-206056500</v>
+        <v>-21451500</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2244922000</v>
+        <v>2292113000</v>
       </c>
       <c r="E3" t="n">
-        <v>-824226000</v>
+        <v>-85806000</v>
       </c>
       <c r="F3" t="n">
-        <v>-824226000</v>
+        <v>-85806000</v>
       </c>
       <c r="G3" t="n">
-        <v>-950538000</v>
+        <v>-302554000</v>
       </c>
       <c r="H3" t="n">
-        <v>730415000</v>
+        <v>619399000</v>
       </c>
       <c r="I3" t="n">
-        <v>21304093000</v>
+        <v>18404027000</v>
       </c>
       <c r="J3" t="n">
-        <v>1420696000</v>
+        <v>2206307000</v>
       </c>
       <c r="K3" t="n">
-        <v>690281000</v>
+        <v>1586908000</v>
       </c>
       <c r="L3" t="n">
-        <v>-974820000</v>
+        <v>-654749000</v>
       </c>
       <c r="M3" t="n">
-        <v>1135141000</v>
+        <v>872179000</v>
       </c>
       <c r="N3" t="n">
-        <v>160321000</v>
+        <v>217430000</v>
       </c>
       <c r="O3" t="n">
-        <v>-332368500</v>
+        <v>-238199500</v>
       </c>
       <c r="P3" t="n">
-        <v>-950538000</v>
+        <v>-160981000</v>
       </c>
       <c r="Q3" t="n">
-        <v>23624322000</v>
+        <v>20465371000</v>
       </c>
       <c r="R3" t="n">
-        <v>687031000</v>
+        <v>1662306000</v>
       </c>
       <c r="S3" t="n">
-        <v>551864890</v>
+        <v>452213068</v>
       </c>
       <c r="T3" t="n">
-        <v>551864890</v>
+        <v>452213068</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.722</v>
+        <v>-0.356</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.722</v>
+        <v>-0.356</v>
       </c>
       <c r="W3" t="n">
-        <v>-950538000</v>
+        <v>-160981000</v>
       </c>
       <c r="X3" t="n">
-        <v>-950538000</v>
+        <v>-160981000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-950538000</v>
+        <v>-160981000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-495089000</v>
+        <v>-569677000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-455449000</v>
+        <v>408696000</v>
       </c>
       <c r="AC3" t="n">
+        <v>141573000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>267123000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>447606000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>714729000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>59830000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>866049000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>64562000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-948942000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>18331000</v>
+      </c>
+      <c r="AL3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>-455449000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>10589000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-444860000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>60035000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-721384000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>29160000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>687293000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>4931000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-974820000</v>
+        <v>-654749000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1135141000</v>
+        <v>872179000</v>
       </c>
       <c r="AO3" t="n">
-        <v>160321000</v>
+        <v>217430000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1221494000</v>
+        <v>1253000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2320229000</v>
+        <v>2061344000</v>
       </c>
       <c r="AR3" t="n">
-        <v>904473000</v>
+        <v>744816000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1598799000</v>
+        <v>1447575000</v>
       </c>
       <c r="AT3" t="n">
-        <v>618040000</v>
+        <v>559709000</v>
       </c>
       <c r="AU3" t="n">
-        <v>980759000</v>
+        <v>887866000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3541723000</v>
+        <v>3314344000</v>
       </c>
       <c r="AW3" t="n">
-        <v>21304093000</v>
+        <v>18404027000</v>
       </c>
       <c r="AX3" t="n">
-        <v>24845816000</v>
+        <v>21718371000</v>
       </c>
       <c r="AY3" t="n">
-        <v>24845816000</v>
+        <v>21718371000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-21451500</v>
+        <v>-206056500</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>2292113000</v>
+        <v>2244922000</v>
       </c>
       <c r="E4" t="n">
-        <v>-85806000</v>
+        <v>-824226000</v>
       </c>
       <c r="F4" t="n">
-        <v>-85806000</v>
+        <v>-824226000</v>
       </c>
       <c r="G4" t="n">
-        <v>-302554000</v>
+        <v>-950538000</v>
       </c>
       <c r="H4" t="n">
-        <v>619399000</v>
+        <v>730415000</v>
       </c>
       <c r="I4" t="n">
-        <v>18404027000</v>
+        <v>21304093000</v>
       </c>
       <c r="J4" t="n">
-        <v>2206307000</v>
+        <v>1420696000</v>
       </c>
       <c r="K4" t="n">
-        <v>1586908000</v>
+        <v>690281000</v>
       </c>
       <c r="L4" t="n">
-        <v>-654749000</v>
+        <v>-974820000</v>
       </c>
       <c r="M4" t="n">
-        <v>872179000</v>
+        <v>1135141000</v>
       </c>
       <c r="N4" t="n">
-        <v>217430000</v>
+        <v>160321000</v>
       </c>
       <c r="O4" t="n">
-        <v>-238199500</v>
+        <v>-332368500</v>
       </c>
       <c r="P4" t="n">
-        <v>-160981000</v>
+        <v>-950538000</v>
       </c>
       <c r="Q4" t="n">
-        <v>20465371000</v>
+        <v>23624322000</v>
       </c>
       <c r="R4" t="n">
-        <v>1662306000</v>
+        <v>687031000</v>
       </c>
       <c r="S4" t="n">
-        <v>452213068</v>
+        <v>551864890</v>
       </c>
       <c r="T4" t="n">
-        <v>452213068</v>
+        <v>551864890</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.356</v>
+        <v>-1.722</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.356</v>
+        <v>-1.722</v>
       </c>
       <c r="W4" t="n">
-        <v>-160981000</v>
+        <v>-950538000</v>
       </c>
       <c r="X4" t="n">
-        <v>-160981000</v>
+        <v>-950538000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-160981000</v>
+        <v>-950538000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-569677000</v>
+        <v>-495089000</v>
       </c>
       <c r="AB4" t="n">
-        <v>408696000</v>
+        <v>-455449000</v>
       </c>
       <c r="AC4" t="n">
-        <v>141573000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>267123000</v>
+        <v>-455449000</v>
       </c>
       <c r="AE4" t="n">
-        <v>447606000</v>
+        <v>10589000</v>
       </c>
       <c r="AF4" t="n">
-        <v>714729000</v>
+        <v>-444860000</v>
       </c>
       <c r="AG4" t="n">
-        <v>59830000</v>
+        <v>60035000</v>
       </c>
       <c r="AH4" t="n">
-        <v>866049000</v>
+        <v>-721384000</v>
       </c>
       <c r="AI4" t="n">
-        <v>64562000</v>
+        <v>29160000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-948942000</v>
+        <v>687293000</v>
       </c>
       <c r="AK4" t="n">
-        <v>18331000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>4931000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-654749000</v>
+        <v>-974820000</v>
       </c>
       <c r="AN4" t="n">
-        <v>872179000</v>
+        <v>1135141000</v>
       </c>
       <c r="AO4" t="n">
-        <v>217430000</v>
+        <v>160321000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1253000000</v>
+        <v>1221494000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2061344000</v>
+        <v>2320229000</v>
       </c>
       <c r="AR4" t="n">
-        <v>744816000</v>
+        <v>904473000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1447575000</v>
+        <v>1598799000</v>
       </c>
       <c r="AT4" t="n">
-        <v>559709000</v>
+        <v>618040000</v>
       </c>
       <c r="AU4" t="n">
-        <v>887866000</v>
+        <v>980759000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3314344000</v>
+        <v>3541723000</v>
       </c>
       <c r="AW4" t="n">
-        <v>18404027000</v>
+        <v>21304093000</v>
       </c>
       <c r="AX4" t="n">
-        <v>21718371000</v>
+        <v>24845816000</v>
       </c>
       <c r="AY4" t="n">
-        <v>21718371000</v>
+        <v>24845816000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-453535500</v>
+        <v>-1881926750</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>829200000</v>
+        <v>2334844000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1814142000</v>
+        <v>-7527707000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1814142000</v>
+        <v>-7527707000</v>
       </c>
       <c r="G5" t="n">
-        <v>-2717093000</v>
+        <v>-6013900000</v>
       </c>
       <c r="H5" t="n">
-        <v>658041000</v>
+        <v>947865000</v>
       </c>
       <c r="I5" t="n">
-        <v>17490747000</v>
+        <v>19654507000</v>
       </c>
       <c r="J5" t="n">
-        <v>-984942000</v>
+        <v>-5192863000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1642983000</v>
+        <v>-6140728000</v>
       </c>
       <c r="L5" t="n">
-        <v>-249358000</v>
+        <v>-863092000</v>
       </c>
       <c r="M5" t="n">
-        <v>452375000</v>
+        <v>997693000</v>
       </c>
       <c r="N5" t="n">
-        <v>203017000</v>
+        <v>134601000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1356486500</v>
+        <v>-368119750</v>
       </c>
       <c r="P5" t="n">
-        <v>-2685344000</v>
+        <v>-6013900000</v>
       </c>
       <c r="Q5" t="n">
-        <v>19369414000</v>
+        <v>21617082000</v>
       </c>
       <c r="R5" t="n">
-        <v>-249004000</v>
+        <v>-6073537000</v>
       </c>
       <c r="S5" t="n">
-        <v>393757406</v>
+        <v>636763934</v>
       </c>
       <c r="T5" t="n">
-        <v>393757406</v>
+        <v>636763934</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.8</v>
+        <v>-9.444000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.8</v>
+        <v>-9.444000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-2685344000</v>
+        <v>-6013900000</v>
       </c>
       <c r="X5" t="n">
-        <v>-2685344000</v>
+        <v>-6013900000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2685344000</v>
+        <v>-6013900000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-349586000</v>
+        <v>1311450000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2335758000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>31749000</v>
-      </c>
+        <v>-7325350000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-2367507000</v>
+        <v>-7325350000</v>
       </c>
       <c r="AE5" t="n">
-        <v>272149000</v>
+        <v>186929000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2095358000</v>
+        <v>-7138421000</v>
       </c>
       <c r="AG5" t="n">
-        <v>60698000</v>
+        <v>65210000</v>
       </c>
       <c r="AH5" t="n">
-        <v>30528000</v>
+        <v>-7428884000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-206201000</v>
+        <v>-7155000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>93588000</v>
+        <v>7198175000</v>
       </c>
       <c r="AK5" t="n">
-        <v>82232000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-147000</v>
-      </c>
+        <v>237864000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-249358000</v>
+        <v>-863092000</v>
       </c>
       <c r="AN5" t="n">
-        <v>452375000</v>
+        <v>997693000</v>
       </c>
       <c r="AO5" t="n">
-        <v>203017000</v>
+        <v>134601000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1416128000</v>
+        <v>1530834000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1878667000</v>
+        <v>1962575000</v>
       </c>
       <c r="AR5" t="n">
-        <v>667782000</v>
+        <v>809474000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1344498000</v>
+        <v>1446076000</v>
       </c>
       <c r="AT5" t="n">
-        <v>512769000</v>
+        <v>619837000</v>
       </c>
       <c r="AU5" t="n">
-        <v>831729000</v>
+        <v>826239000</v>
       </c>
       <c r="AV5" t="n">
-        <v>3294795000</v>
+        <v>3493409000</v>
       </c>
       <c r="AW5" t="n">
-        <v>17490747000</v>
+        <v>19654507000</v>
       </c>
       <c r="AX5" t="n">
-        <v>20785542000</v>
+        <v>23147916000</v>
       </c>
       <c r="AY5" t="n">
-        <v>20785542000</v>
-      </c>
+        <v>23147916000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>636763934</v>
+      </c>
+      <c r="T6" t="n">
+        <v>636763934</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.164</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.164</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1702,938 +1757,938 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>636763934</v>
+        <v>394107834</v>
       </c>
       <c r="C2" t="n">
-        <v>636763934</v>
+        <v>394107834</v>
       </c>
       <c r="D2" t="n">
-        <v>4973729000</v>
+        <v>3909572000</v>
       </c>
       <c r="E2" t="n">
-        <v>11945404000</v>
+        <v>9648839000</v>
       </c>
       <c r="F2" t="n">
-        <v>6260292000</v>
+        <v>11941492000</v>
       </c>
       <c r="G2" t="n">
-        <v>19664675000</v>
+        <v>23474760000</v>
       </c>
       <c r="H2" t="n">
-        <v>2656423000</v>
+        <v>1603925000</v>
       </c>
       <c r="I2" t="n">
-        <v>6260292000</v>
+        <v>11941492000</v>
       </c>
       <c r="J2" t="n">
-        <v>183569000</v>
+        <v>354758000</v>
       </c>
       <c r="K2" t="n">
-        <v>7902840000</v>
+        <v>14180679000</v>
       </c>
       <c r="L2" t="n">
-        <v>13304825000</v>
+        <v>16117551000</v>
       </c>
       <c r="M2" t="n">
-        <v>14603575000</v>
+        <v>17995855000</v>
       </c>
       <c r="N2" t="n">
-        <v>6700735000</v>
+        <v>3815176000</v>
       </c>
       <c r="O2" t="n">
-        <v>7902840000</v>
+        <v>14180679000</v>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>-10644057000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>17760800000</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>269500000</v>
+        <v>160872000</v>
       </c>
       <c r="T2" t="n">
-        <v>269500000</v>
+        <v>160872000</v>
       </c>
       <c r="U2" t="n">
-        <v>30444482000</v>
+        <v>27604447000</v>
       </c>
       <c r="V2" t="n">
-        <v>8351999000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>4456551000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>676577000</v>
+        <v>200477000</v>
       </c>
       <c r="Y2" t="n">
-        <v>877690000</v>
+        <v>1162465000</v>
       </c>
       <c r="Z2" t="n">
-        <v>5537713000</v>
+        <v>2244825000</v>
       </c>
       <c r="AA2" t="n">
-        <v>135728000</v>
+        <v>307953000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5401985000</v>
+        <v>1936872000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1260019000</v>
+        <v>848784000</v>
       </c>
       <c r="AD2" t="n">
-        <v>22092483000</v>
+        <v>23147896000</v>
       </c>
       <c r="AE2" t="n">
-        <v>6407691000</v>
+        <v>7404014000</v>
       </c>
       <c r="AF2" t="n">
-        <v>47841000</v>
+        <v>46805000</v>
       </c>
       <c r="AG2" t="n">
-        <v>6359850000</v>
+        <v>7357209000</v>
       </c>
       <c r="AH2" t="n">
-        <v>908794000</v>
+        <v>863250000</v>
       </c>
       <c r="AI2" t="n">
-        <v>12182723000</v>
+        <v>11162649000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2468605000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>3101291000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>89002000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>306963000</v>
+        <v>957424000</v>
       </c>
       <c r="AM2" t="n">
-        <v>9407155000</v>
+        <v>7014932000</v>
       </c>
       <c r="AN2" t="n">
-        <v>45048057000</v>
+        <v>45600302000</v>
       </c>
       <c r="AO2" t="n">
-        <v>20299151000</v>
+        <v>20848481000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>47549000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>666344000</v>
+        <v>776758000</v>
       </c>
       <c r="AR2" t="n">
-        <v>18506000</v>
+        <v>38324000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2212452000</v>
+        <v>4330691000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2212452000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>4330691000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>402124000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>605736000</v>
+        <v>606722000</v>
       </c>
       <c r="AW2" t="n">
-        <v>143998000</v>
+        <v>281468000</v>
       </c>
       <c r="AX2" t="n">
-        <v>461738000</v>
+        <v>325254000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2795588000</v>
+        <v>5050852000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1642548000</v>
+        <v>2239187000</v>
       </c>
       <c r="BA2" t="n">
-        <v>138731000</v>
+        <v>359018000</v>
       </c>
       <c r="BB2" t="n">
-        <v>1503817000</v>
+        <v>1880169000</v>
       </c>
       <c r="BC2" t="n">
-        <v>12116141000</v>
+        <v>7709938000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-7502804000</v>
+        <v>-5976631000</v>
       </c>
       <c r="BE2" t="n">
-        <v>19618945000</v>
+        <v>13686569000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2069255000</v>
+        <v>1347091000</v>
       </c>
       <c r="BG2" t="n">
-        <v>342848000</v>
+        <v>1330564000</v>
       </c>
       <c r="BH2" t="n">
-        <v>11658069000</v>
+        <v>6882968000</v>
       </c>
       <c r="BI2" t="n">
-        <v>255493000</v>
+        <v>382041000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>5293280000</v>
+        <v>3743905000</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>24748906000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+        <v>24751821000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>112809000</v>
+      </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>412962000</v>
+        <v>1463557000</v>
       </c>
       <c r="BP2" t="n">
-        <v>6056212000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+        <v>6135043000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5210362000</v>
+      </c>
       <c r="BR2" t="n">
-        <v>2548333000</v>
+        <v>2998772000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2730087000</v>
+        <v>2570242000</v>
       </c>
       <c r="BT2" t="n">
-        <v>777792000</v>
+        <v>566029000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1802939000</v>
+        <v>3118821000</v>
       </c>
       <c r="BV2" t="n">
-        <v>6180845000</v>
+        <v>4471744000</v>
       </c>
       <c r="BW2" t="n">
-        <v>-3833695000</v>
+        <v>-605693000</v>
       </c>
       <c r="BX2" t="n">
-        <v>10014540000</v>
+        <v>5077437000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10295948000</v>
+        <v>9562656000</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3507842000</v>
+        <v>4178147000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6788106000</v>
+        <v>5384509000</v>
       </c>
       <c r="CB2" t="n">
-        <v>6788106000</v>
+        <v>5384509000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>636763934</v>
+        <v>530643934</v>
       </c>
       <c r="C3" t="n">
-        <v>636763934</v>
+        <v>530643934</v>
       </c>
       <c r="D3" t="n">
-        <v>5208046000</v>
+        <v>3461749000</v>
       </c>
       <c r="E3" t="n">
-        <v>14496194000</v>
+        <v>12942317000</v>
       </c>
       <c r="F3" t="n">
-        <v>9181526000</v>
+        <v>10246120000</v>
       </c>
       <c r="G3" t="n">
-        <v>25384243000</v>
+        <v>24959105000</v>
       </c>
       <c r="H3" t="n">
-        <v>1752822000</v>
+        <v>3777917000</v>
       </c>
       <c r="I3" t="n">
-        <v>9181526000</v>
+        <v>10246120000</v>
       </c>
       <c r="J3" t="n">
-        <v>15980000</v>
+        <v>22255000</v>
       </c>
       <c r="K3" t="n">
-        <v>10904029000</v>
+        <v>12039043000</v>
       </c>
       <c r="L3" t="n">
-        <v>15681247000</v>
+        <v>16350256000</v>
       </c>
       <c r="M3" t="n">
-        <v>17438010000</v>
+        <v>18120248000</v>
       </c>
       <c r="N3" t="n">
-        <v>6533981000</v>
+        <v>6081205000</v>
       </c>
       <c r="O3" t="n">
-        <v>10904029000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>12039043000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-35258000</v>
+      </c>
       <c r="Q3" t="n">
-        <v>-4823505000</v>
+        <v>-3789798000</v>
       </c>
       <c r="R3" t="n">
-        <v>17760800000</v>
+        <v>17637010000</v>
       </c>
       <c r="S3" t="n">
-        <v>269500000</v>
+        <v>219904000</v>
       </c>
       <c r="T3" t="n">
-        <v>269500000</v>
+        <v>219904000</v>
       </c>
       <c r="U3" t="n">
-        <v>37072084000</v>
+        <v>37109586000</v>
       </c>
       <c r="V3" t="n">
-        <v>7560941000</v>
+        <v>6928074000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>475164000</v>
+        <v>303077000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1175460000</v>
+        <v>1184165000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4785847000</v>
+        <v>4326103000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8629000</v>
+        <v>14890000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4777218000</v>
+        <v>4311213000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1124470000</v>
+        <v>1114729000</v>
       </c>
       <c r="AD3" t="n">
-        <v>29511143000</v>
+        <v>30181512000</v>
       </c>
       <c r="AE3" t="n">
-        <v>9710347000</v>
+        <v>8616214000</v>
       </c>
       <c r="AF3" t="n">
-        <v>7351000</v>
+        <v>7365000</v>
       </c>
       <c r="AG3" t="n">
-        <v>9702996000</v>
+        <v>8608849000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1144479000</v>
+        <v>988395000</v>
       </c>
       <c r="AI3" t="n">
-        <v>10648163000</v>
+        <v>13271025000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2245033000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>1864965000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
       <c r="AL3" t="n">
-        <v>777965000</v>
+        <v>1018456000</v>
       </c>
       <c r="AM3" t="n">
-        <v>7625165000</v>
+        <v>10387604000</v>
       </c>
       <c r="AN3" t="n">
-        <v>54510094000</v>
+        <v>55229834000</v>
       </c>
       <c r="AO3" t="n">
-        <v>23246129000</v>
+        <v>21270405000</v>
       </c>
       <c r="AP3" t="n">
         <v>5890000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1325068000</v>
+        <v>1065817000</v>
       </c>
       <c r="AR3" t="n">
-        <v>27995000</v>
+        <v>35076000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2086629000</v>
+        <v>2484221000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2086629000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>2484221000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>422676000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>643491000</v>
+        <v>670086000</v>
       </c>
       <c r="AW3" t="n">
-        <v>303902000</v>
+        <v>290756000</v>
       </c>
       <c r="AX3" t="n">
-        <v>339589000</v>
+        <v>379330000</v>
       </c>
       <c r="AY3" t="n">
-        <v>5467699000</v>
+        <v>5047272000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1722503000</v>
+        <v>1792923000</v>
       </c>
       <c r="BA3" t="n">
-        <v>218686000</v>
+        <v>289106000</v>
       </c>
       <c r="BB3" t="n">
         <v>1503817000</v>
       </c>
       <c r="BC3" t="n">
-        <v>11681398000</v>
+        <v>9873555000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-6892050000</v>
+        <v>-6350033000</v>
       </c>
       <c r="BE3" t="n">
-        <v>18573448000</v>
+        <v>16223588000</v>
       </c>
       <c r="BF3" t="n">
-        <v>2559952000</v>
+        <v>2399723000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1515961000</v>
+        <v>1520010000</v>
       </c>
       <c r="BH3" t="n">
-        <v>9744732000</v>
+        <v>7550017000</v>
       </c>
       <c r="BI3" t="n">
         <v>28076000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>4724727000</v>
+        <v>4725762000</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>31263965000</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
+        <v>33959429000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>56281000</v>
+      </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>2021370000</v>
+        <v>1972634000</v>
       </c>
       <c r="BP3" t="n">
-        <v>6600502000</v>
-      </c>
-      <c r="BQ3" t="inlineStr"/>
+        <v>7582666000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6932870000</v>
+      </c>
       <c r="BR3" t="n">
-        <v>3097195000</v>
+        <v>2891315000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2677781000</v>
+        <v>3712196000</v>
       </c>
       <c r="BT3" t="n">
-        <v>825526000</v>
+        <v>979155000</v>
       </c>
       <c r="BU3" t="n">
-        <v>2534302000</v>
+        <v>2472029000</v>
       </c>
       <c r="BV3" t="n">
-        <v>8524702000</v>
+        <v>7128370000</v>
       </c>
       <c r="BW3" t="n">
-        <v>-692460000</v>
+        <v>-714586000</v>
       </c>
       <c r="BX3" t="n">
-        <v>9217162000</v>
+        <v>7842956000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11583089000</v>
+        <v>14803730000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2310921000</v>
+        <v>5345417000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9272168000</v>
+        <v>9458313000</v>
       </c>
       <c r="CB3" t="n">
-        <v>9272168000</v>
+        <v>9458313000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>530643934</v>
+        <v>636763934</v>
       </c>
       <c r="C4" t="n">
-        <v>530643934</v>
+        <v>636763934</v>
       </c>
       <c r="D4" t="n">
-        <v>3461749000</v>
+        <v>5208046000</v>
       </c>
       <c r="E4" t="n">
-        <v>12942317000</v>
+        <v>14496194000</v>
       </c>
       <c r="F4" t="n">
-        <v>10246120000</v>
+        <v>9181526000</v>
       </c>
       <c r="G4" t="n">
-        <v>24959105000</v>
+        <v>25384243000</v>
       </c>
       <c r="H4" t="n">
-        <v>3777917000</v>
+        <v>1752822000</v>
       </c>
       <c r="I4" t="n">
-        <v>10246120000</v>
+        <v>9181526000</v>
       </c>
       <c r="J4" t="n">
-        <v>22255000</v>
+        <v>15980000</v>
       </c>
       <c r="K4" t="n">
-        <v>12039043000</v>
+        <v>10904029000</v>
       </c>
       <c r="L4" t="n">
-        <v>16350256000</v>
+        <v>15681247000</v>
       </c>
       <c r="M4" t="n">
-        <v>18120248000</v>
+        <v>17438010000</v>
       </c>
       <c r="N4" t="n">
-        <v>6081205000</v>
+        <v>6533981000</v>
       </c>
       <c r="O4" t="n">
-        <v>12039043000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-35258000</v>
-      </c>
+        <v>10904029000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-3789798000</v>
+        <v>-4823505000</v>
       </c>
       <c r="R4" t="n">
-        <v>17637010000</v>
+        <v>17760800000</v>
       </c>
       <c r="S4" t="n">
-        <v>219904000</v>
+        <v>269500000</v>
       </c>
       <c r="T4" t="n">
-        <v>219904000</v>
+        <v>269500000</v>
       </c>
       <c r="U4" t="n">
-        <v>37109586000</v>
+        <v>37072084000</v>
       </c>
       <c r="V4" t="n">
-        <v>6928074000</v>
+        <v>7560941000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>303077000</v>
+        <v>475164000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1184165000</v>
+        <v>1175460000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4326103000</v>
+        <v>4785847000</v>
       </c>
       <c r="AA4" t="n">
-        <v>14890000</v>
+        <v>8629000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4311213000</v>
+        <v>4777218000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1114729000</v>
+        <v>1124470000</v>
       </c>
       <c r="AD4" t="n">
-        <v>30181512000</v>
+        <v>29511143000</v>
       </c>
       <c r="AE4" t="n">
-        <v>8616214000</v>
+        <v>9710347000</v>
       </c>
       <c r="AF4" t="n">
-        <v>7365000</v>
+        <v>7351000</v>
       </c>
       <c r="AG4" t="n">
-        <v>8608849000</v>
+        <v>9702996000</v>
       </c>
       <c r="AH4" t="n">
-        <v>988395000</v>
+        <v>1144479000</v>
       </c>
       <c r="AI4" t="n">
-        <v>13271025000</v>
+        <v>10648163000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1864965000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+        <v>2245033000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>1018456000</v>
+        <v>777965000</v>
       </c>
       <c r="AM4" t="n">
-        <v>10387604000</v>
+        <v>7625165000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55229834000</v>
+        <v>54510094000</v>
       </c>
       <c r="AO4" t="n">
-        <v>21270405000</v>
+        <v>23246129000</v>
       </c>
       <c r="AP4" t="n">
         <v>5890000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1065817000</v>
+        <v>1325068000</v>
       </c>
       <c r="AR4" t="n">
-        <v>35076000</v>
+        <v>27995000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2484221000</v>
+        <v>2086629000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2484221000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>422676000</v>
-      </c>
+        <v>2086629000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>670086000</v>
+        <v>643491000</v>
       </c>
       <c r="AW4" t="n">
-        <v>290756000</v>
+        <v>303902000</v>
       </c>
       <c r="AX4" t="n">
-        <v>379330000</v>
+        <v>339589000</v>
       </c>
       <c r="AY4" t="n">
-        <v>5047272000</v>
+        <v>5467699000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1792923000</v>
+        <v>1722503000</v>
       </c>
       <c r="BA4" t="n">
-        <v>289106000</v>
+        <v>218686000</v>
       </c>
       <c r="BB4" t="n">
         <v>1503817000</v>
       </c>
       <c r="BC4" t="n">
-        <v>9873555000</v>
+        <v>11681398000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-6350033000</v>
+        <v>-6892050000</v>
       </c>
       <c r="BE4" t="n">
-        <v>16223588000</v>
+        <v>18573448000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2399723000</v>
+        <v>2559952000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1520010000</v>
+        <v>1515961000</v>
       </c>
       <c r="BH4" t="n">
-        <v>7550017000</v>
+        <v>9744732000</v>
       </c>
       <c r="BI4" t="n">
         <v>28076000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4725762000</v>
+        <v>4724727000</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>33959429000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>56281000</v>
-      </c>
+        <v>31263965000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1972634000</v>
+        <v>2021370000</v>
       </c>
       <c r="BP4" t="n">
-        <v>7582666000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6932870000</v>
-      </c>
+        <v>6600502000</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
-        <v>2891315000</v>
+        <v>3097195000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3712196000</v>
+        <v>2677781000</v>
       </c>
       <c r="BT4" t="n">
-        <v>979155000</v>
+        <v>825526000</v>
       </c>
       <c r="BU4" t="n">
-        <v>2472029000</v>
+        <v>2534302000</v>
       </c>
       <c r="BV4" t="n">
-        <v>7128370000</v>
+        <v>8524702000</v>
       </c>
       <c r="BW4" t="n">
-        <v>-714586000</v>
+        <v>-692460000</v>
       </c>
       <c r="BX4" t="n">
-        <v>7842956000</v>
+        <v>9217162000</v>
       </c>
       <c r="BY4" t="n">
-        <v>14803730000</v>
+        <v>11583089000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5345417000</v>
+        <v>2310921000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9458313000</v>
+        <v>9272168000</v>
       </c>
       <c r="CB4" t="n">
-        <v>9458313000</v>
+        <v>9272168000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>394107834</v>
+        <v>636763934</v>
       </c>
       <c r="C5" t="n">
-        <v>394107834</v>
+        <v>636763934</v>
       </c>
       <c r="D5" t="n">
-        <v>3909572000</v>
+        <v>4973729000</v>
       </c>
       <c r="E5" t="n">
-        <v>9648839000</v>
+        <v>11945404000</v>
       </c>
       <c r="F5" t="n">
-        <v>11941492000</v>
+        <v>6260292000</v>
       </c>
       <c r="G5" t="n">
-        <v>23474760000</v>
+        <v>19664675000</v>
       </c>
       <c r="H5" t="n">
-        <v>1603925000</v>
+        <v>2656423000</v>
       </c>
       <c r="I5" t="n">
-        <v>11941492000</v>
+        <v>6260292000</v>
       </c>
       <c r="J5" t="n">
-        <v>354758000</v>
+        <v>183569000</v>
       </c>
       <c r="K5" t="n">
-        <v>14180679000</v>
+        <v>7902840000</v>
       </c>
       <c r="L5" t="n">
-        <v>16117551000</v>
+        <v>13304825000</v>
       </c>
       <c r="M5" t="n">
-        <v>17995855000</v>
+        <v>14603575000</v>
       </c>
       <c r="N5" t="n">
-        <v>3815176000</v>
+        <v>6700735000</v>
       </c>
       <c r="O5" t="n">
-        <v>14180679000</v>
+        <v>7902840000</v>
       </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>-10644057000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>17760800000</v>
+      </c>
       <c r="S5" t="n">
-        <v>160872000</v>
+        <v>269500000</v>
       </c>
       <c r="T5" t="n">
-        <v>160872000</v>
+        <v>269500000</v>
       </c>
       <c r="U5" t="n">
-        <v>27604447000</v>
+        <v>30444482000</v>
       </c>
       <c r="V5" t="n">
-        <v>4456551000</v>
-      </c>
-      <c r="W5" t="n">
+        <v>8351999000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>676577000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>877690000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5537713000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>135728000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5401985000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1260019000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22092483000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>6407691000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>47841000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6359850000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>908794000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>12182723000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2468605000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>306963000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>9407155000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>45048057000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>20299151000</v>
+      </c>
+      <c r="AP5" t="n">
         <v>0</v>
       </c>
-      <c r="X5" t="n">
-        <v>200477000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1162465000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2244825000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>307953000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1936872000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>848784000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>23147896000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>7404014000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>46805000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>7357209000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>863250000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>11162649000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3101291000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>89002000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>957424000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>7014932000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>45600302000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>20848481000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>47549000</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>776758000</v>
+        <v>666344000</v>
       </c>
       <c r="AR5" t="n">
-        <v>38324000</v>
+        <v>18506000</v>
       </c>
       <c r="AS5" t="n">
-        <v>4330691000</v>
+        <v>2212452000</v>
       </c>
       <c r="AT5" t="n">
-        <v>4330691000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>402124000</v>
-      </c>
+        <v>2212452000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>606722000</v>
+        <v>605736000</v>
       </c>
       <c r="AW5" t="n">
-        <v>281468000</v>
+        <v>143998000</v>
       </c>
       <c r="AX5" t="n">
-        <v>325254000</v>
+        <v>461738000</v>
       </c>
       <c r="AY5" t="n">
-        <v>5050852000</v>
+        <v>2795588000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2239187000</v>
+        <v>1642548000</v>
       </c>
       <c r="BA5" t="n">
-        <v>359018000</v>
+        <v>138731000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1880169000</v>
+        <v>1503817000</v>
       </c>
       <c r="BC5" t="n">
-        <v>7709938000</v>
+        <v>12116141000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-5976631000</v>
+        <v>-7502804000</v>
       </c>
       <c r="BE5" t="n">
-        <v>13686569000</v>
+        <v>19618945000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1347091000</v>
+        <v>2069255000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1330564000</v>
+        <v>342848000</v>
       </c>
       <c r="BH5" t="n">
-        <v>6882968000</v>
+        <v>11658069000</v>
       </c>
       <c r="BI5" t="n">
-        <v>382041000</v>
+        <v>255493000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3743905000</v>
+        <v>5293280000</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>24751821000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>112809000</v>
-      </c>
+        <v>24748906000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1463557000</v>
+        <v>412962000</v>
       </c>
       <c r="BP5" t="n">
-        <v>6135043000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5210362000</v>
-      </c>
+        <v>6056212000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
-        <v>2998772000</v>
+        <v>2548333000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2570242000</v>
+        <v>2730087000</v>
       </c>
       <c r="BT5" t="n">
-        <v>566029000</v>
+        <v>777792000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3118821000</v>
+        <v>1802939000</v>
       </c>
       <c r="BV5" t="n">
-        <v>4471744000</v>
+        <v>6180845000</v>
       </c>
       <c r="BW5" t="n">
-        <v>-605693000</v>
+        <v>-3833695000</v>
       </c>
       <c r="BX5" t="n">
-        <v>5077437000</v>
+        <v>10014540000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9562656000</v>
+        <v>10295948000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4178147000</v>
+        <v>3507842000</v>
       </c>
       <c r="CA5" t="n">
-        <v>5384509000</v>
+        <v>6788106000</v>
       </c>
       <c r="CB5" t="n">
-        <v>5384509000</v>
+        <v>6788106000</v>
       </c>
     </row>
   </sheetData>
@@ -2919,43 +2974,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2253005000</v>
+        <v>-2195899000</v>
       </c>
       <c r="C2" t="n">
-        <v>-7185429000</v>
+        <v>-4254292000</v>
       </c>
       <c r="D2" t="n">
-        <v>6992027000</v>
+        <v>6394196000</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-2138339000</v>
+        <v>-1156141000</v>
       </c>
       <c r="G2" t="n">
-        <v>3965148000</v>
+        <v>3473102000</v>
       </c>
       <c r="H2" t="n">
-        <v>5693844000</v>
+        <v>2490570000</v>
       </c>
       <c r="I2" t="n">
-        <v>11434000</v>
+        <v>-20711000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1740130000</v>
+        <v>1003243000</v>
       </c>
       <c r="K2" t="n">
-        <v>-898422000</v>
+        <v>2602983000</v>
       </c>
       <c r="L2" t="n">
-        <v>19941000</v>
+        <v>1000000000</v>
       </c>
       <c r="M2" t="n">
-        <v>-602671000</v>
+        <v>-491625000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -2964,478 +3019,480 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-193402000</v>
+        <v>2139904000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-193402000</v>
+        <v>2139904000</v>
       </c>
       <c r="R2" t="n">
-        <v>-7185429000</v>
+        <v>-4254292000</v>
       </c>
       <c r="S2" t="n">
-        <v>6992027000</v>
+        <v>6394196000</v>
       </c>
       <c r="T2" t="n">
-        <v>-727042000</v>
+        <v>-559982000</v>
       </c>
       <c r="U2" t="n">
-        <v>1048004000</v>
+        <v>-84063000</v>
       </c>
       <c r="V2" t="n">
-        <v>137222000</v>
+        <v>77563000</v>
       </c>
       <c r="W2" t="n">
-        <v>6584000</v>
+        <v>50000000</v>
       </c>
       <c r="X2" t="n">
-        <v>19768000</v>
+        <v>-558543000</v>
       </c>
       <c r="Y2" t="n">
-        <v>39768000</v>
+        <v>1011457000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-20000000</v>
+        <v>-1570000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>34413000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>34413000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>53968000</v>
+        <v>167154000</v>
       </c>
       <c r="AD2" t="n">
-        <v>68968000</v>
+        <v>182154000</v>
       </c>
       <c r="AE2" t="n">
         <v>-15000000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-32000</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>-32000</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2032969000</v>
+        <v>-1121948000</v>
       </c>
       <c r="AI2" t="n">
-        <v>105338000</v>
+        <v>34193000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2138307000</v>
+        <v>-1156141000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-114666000</v>
+        <v>-1039758000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-185176000</v>
+        <v>-409241000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2446048000</v>
+        <v>-2830406000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3733000</v>
+        <v>3182000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1975488000</v>
+        <v>-771435000</v>
       </c>
       <c r="AP2" t="n">
-        <v>417580000</v>
+        <v>-1670971000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-4742713000</v>
+        <v>-1152141000</v>
       </c>
       <c r="AR2" t="n">
-        <v>793421000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>254271000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>947865000</v>
+        <v>658041000</v>
       </c>
       <c r="AV2" t="n">
-        <v>70307000</v>
+        <v>70996000</v>
       </c>
       <c r="AW2" t="n">
-        <v>877558000</v>
+        <v>587045000</v>
       </c>
       <c r="AX2" t="n">
-        <v>502632000</v>
+        <v>1748599000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-168462000</v>
+        <v>58554000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-9727000</v>
+        <v>-5196000</v>
       </c>
       <c r="BA2" t="n">
-        <v>2572000</v>
+        <v>-201005000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-7138421000</v>
+        <v>-2052080000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1737026000</v>
+        <v>-1921941000</v>
       </c>
       <c r="C3" t="n">
-        <v>-6645444000</v>
+        <v>-6068695000</v>
       </c>
       <c r="D3" t="n">
-        <v>8185847000</v>
+        <v>9622034000</v>
       </c>
       <c r="E3" t="n">
-        <v>173581000</v>
+        <v>624126000</v>
       </c>
       <c r="F3" t="n">
-        <v>-2523814000</v>
+        <v>-2644109000</v>
       </c>
       <c r="G3" t="n">
-        <v>5693844000</v>
+        <v>4533808000</v>
       </c>
       <c r="H3" t="n">
-        <v>4533808000</v>
+        <v>3473102000</v>
       </c>
       <c r="I3" t="n">
-        <v>19295000</v>
+        <v>80890000</v>
       </c>
       <c r="J3" t="n">
-        <v>1140741000</v>
+        <v>979816000</v>
       </c>
       <c r="K3" t="n">
-        <v>852473000</v>
+        <v>5898551000</v>
       </c>
       <c r="L3" t="n">
-        <v>11479000</v>
+        <v>2512132000</v>
       </c>
       <c r="M3" t="n">
-        <v>-866141000</v>
+        <v>-680942000</v>
       </c>
       <c r="N3" t="n">
-        <v>173581000</v>
+        <v>624126000</v>
       </c>
       <c r="O3" t="n">
-        <v>173581000</v>
+        <v>624126000</v>
       </c>
       <c r="P3" t="n">
-        <v>1540403000</v>
+        <v>3553339000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1540403000</v>
+        <v>3553339000</v>
       </c>
       <c r="R3" t="n">
-        <v>-6645444000</v>
+        <v>-6068695000</v>
       </c>
       <c r="S3" t="n">
-        <v>8185847000</v>
+        <v>9622034000</v>
       </c>
       <c r="T3" t="n">
-        <v>-498520000</v>
+        <v>-5640903000</v>
       </c>
       <c r="U3" t="n">
-        <v>1570855000</v>
+        <v>-3057413000</v>
       </c>
       <c r="V3" t="n">
-        <v>162926000</v>
+        <v>272941000</v>
       </c>
       <c r="W3" t="n">
-        <v>18005000</v>
+        <v>19005000</v>
       </c>
       <c r="X3" t="n">
-        <v>71350000</v>
+        <v>-994830000</v>
       </c>
       <c r="Y3" t="n">
-        <v>232266000</v>
+        <v>683269000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-160916000</v>
+        <v>-1678099000</v>
       </c>
       <c r="AA3" t="n">
-        <v>44409000</v>
+        <v>2040000</v>
       </c>
       <c r="AB3" t="n">
-        <v>44409000</v>
+        <v>2040000</v>
       </c>
       <c r="AC3" t="n">
-        <v>39843000</v>
+        <v>104109000</v>
       </c>
       <c r="AD3" t="n">
-        <v>39843000</v>
+        <v>191038000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
+        <v>-86929000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-2449743000</v>
+        <v>-2624434000</v>
       </c>
       <c r="AI3" t="n">
-        <v>74071000</v>
+        <v>19675000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2523814000</v>
+        <v>-2644109000</v>
       </c>
       <c r="AK3" t="n">
-        <v>786788000</v>
+        <v>722168000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-354755000</v>
+        <v>-347989000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1017831000</v>
+        <v>-1266848000</v>
       </c>
       <c r="AN3" t="n">
-        <v>11355000</v>
+        <v>-13351000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2141804000</v>
+        <v>4412898000</v>
       </c>
       <c r="AP3" t="n">
-        <v>325499000</v>
+        <v>-1938272000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>621294000</v>
+        <v>-4119213000</v>
       </c>
       <c r="AR3" t="n">
-        <v>974186000</v>
+        <v>577711000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>730415000</v>
+        <v>619399000</v>
       </c>
       <c r="AV3" t="n">
-        <v>70420000</v>
+        <v>69912000</v>
       </c>
       <c r="AW3" t="n">
-        <v>659995000</v>
+        <v>549487000</v>
       </c>
       <c r="AX3" t="n">
-        <v>123492000</v>
+        <v>899585000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-123481000</v>
+        <v>-191828000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>578000</v>
+        <v>-1123000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-10284000</v>
+        <v>-8026000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-444860000</v>
+        <v>857321000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1921941000</v>
+        <v>-1737026000</v>
       </c>
       <c r="C4" t="n">
-        <v>-6068695000</v>
+        <v>-6645444000</v>
       </c>
       <c r="D4" t="n">
-        <v>9622034000</v>
+        <v>8185847000</v>
       </c>
       <c r="E4" t="n">
-        <v>624126000</v>
+        <v>173581000</v>
       </c>
       <c r="F4" t="n">
-        <v>-2644109000</v>
+        <v>-2523814000</v>
       </c>
       <c r="G4" t="n">
+        <v>5693844000</v>
+      </c>
+      <c r="H4" t="n">
         <v>4533808000</v>
       </c>
-      <c r="H4" t="n">
-        <v>3473102000</v>
-      </c>
       <c r="I4" t="n">
-        <v>80890000</v>
+        <v>19295000</v>
       </c>
       <c r="J4" t="n">
-        <v>979816000</v>
+        <v>1140741000</v>
       </c>
       <c r="K4" t="n">
-        <v>5898551000</v>
+        <v>852473000</v>
       </c>
       <c r="L4" t="n">
-        <v>2512132000</v>
+        <v>11479000</v>
       </c>
       <c r="M4" t="n">
-        <v>-680942000</v>
+        <v>-866141000</v>
       </c>
       <c r="N4" t="n">
-        <v>624126000</v>
+        <v>173581000</v>
       </c>
       <c r="O4" t="n">
-        <v>624126000</v>
+        <v>173581000</v>
       </c>
       <c r="P4" t="n">
-        <v>3553339000</v>
+        <v>1540403000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3553339000</v>
+        <v>1540403000</v>
       </c>
       <c r="R4" t="n">
-        <v>-6068695000</v>
+        <v>-6645444000</v>
       </c>
       <c r="S4" t="n">
-        <v>9622034000</v>
+        <v>8185847000</v>
       </c>
       <c r="T4" t="n">
-        <v>-5640903000</v>
+        <v>-498520000</v>
       </c>
       <c r="U4" t="n">
-        <v>-3057413000</v>
+        <v>1570855000</v>
       </c>
       <c r="V4" t="n">
-        <v>272941000</v>
+        <v>162926000</v>
       </c>
       <c r="W4" t="n">
-        <v>19005000</v>
+        <v>18005000</v>
       </c>
       <c r="X4" t="n">
-        <v>-994830000</v>
+        <v>71350000</v>
       </c>
       <c r="Y4" t="n">
-        <v>683269000</v>
+        <v>232266000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1678099000</v>
+        <v>-160916000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2040000</v>
+        <v>44409000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2040000</v>
+        <v>44409000</v>
       </c>
       <c r="AC4" t="n">
-        <v>104109000</v>
+        <v>39843000</v>
       </c>
       <c r="AD4" t="n">
-        <v>191038000</v>
+        <v>39843000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-86929000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4" t="n">
-        <v>-2624434000</v>
+        <v>-2449743000</v>
       </c>
       <c r="AI4" t="n">
-        <v>19675000</v>
+        <v>74071000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2644109000</v>
+        <v>-2523814000</v>
       </c>
       <c r="AK4" t="n">
-        <v>722168000</v>
+        <v>786788000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-347989000</v>
+        <v>-354755000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1266848000</v>
+        <v>-1017831000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-13351000</v>
+        <v>11355000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4412898000</v>
+        <v>-2141804000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1938272000</v>
+        <v>325499000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-4119213000</v>
+        <v>621294000</v>
       </c>
       <c r="AR4" t="n">
-        <v>577711000</v>
+        <v>974186000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>619399000</v>
+        <v>730415000</v>
       </c>
       <c r="AV4" t="n">
-        <v>69912000</v>
+        <v>70420000</v>
       </c>
       <c r="AW4" t="n">
-        <v>549487000</v>
+        <v>659995000</v>
       </c>
       <c r="AX4" t="n">
-        <v>899585000</v>
+        <v>123492000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-191828000</v>
+        <v>-123481000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1123000</v>
+        <v>578000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-8026000</v>
+        <v>-10284000</v>
       </c>
       <c r="BB4" t="n">
-        <v>857321000</v>
+        <v>-444860000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2195899000</v>
+        <v>-2253005000</v>
       </c>
       <c r="C5" t="n">
-        <v>-4254292000</v>
+        <v>-7185429000</v>
       </c>
       <c r="D5" t="n">
-        <v>6394196000</v>
+        <v>6992027000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1156141000</v>
+        <v>-2138339000</v>
       </c>
       <c r="G5" t="n">
-        <v>3473102000</v>
+        <v>3965148000</v>
       </c>
       <c r="H5" t="n">
-        <v>2490570000</v>
+        <v>5693844000</v>
       </c>
       <c r="I5" t="n">
-        <v>-20711000</v>
+        <v>11434000</v>
       </c>
       <c r="J5" t="n">
-        <v>1003243000</v>
+        <v>-1740130000</v>
       </c>
       <c r="K5" t="n">
-        <v>2602983000</v>
+        <v>-898422000</v>
       </c>
       <c r="L5" t="n">
-        <v>1000000000</v>
+        <v>19941000</v>
       </c>
       <c r="M5" t="n">
-        <v>-491625000</v>
+        <v>-602671000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3444,119 +3501,117 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2139904000</v>
+        <v>-193402000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2139904000</v>
+        <v>-193402000</v>
       </c>
       <c r="R5" t="n">
-        <v>-4254292000</v>
+        <v>-7185429000</v>
       </c>
       <c r="S5" t="n">
-        <v>6394196000</v>
+        <v>6992027000</v>
       </c>
       <c r="T5" t="n">
-        <v>-559982000</v>
+        <v>-727042000</v>
       </c>
       <c r="U5" t="n">
-        <v>-84063000</v>
+        <v>1048004000</v>
       </c>
       <c r="V5" t="n">
-        <v>77563000</v>
+        <v>137222000</v>
       </c>
       <c r="W5" t="n">
-        <v>50000000</v>
+        <v>6584000</v>
       </c>
       <c r="X5" t="n">
-        <v>-558543000</v>
+        <v>19768000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1011457000</v>
+        <v>39768000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1570000000</v>
+        <v>-20000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>34413000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>34413000</v>
       </c>
       <c r="AC5" t="n">
-        <v>167154000</v>
+        <v>53968000</v>
       </c>
       <c r="AD5" t="n">
-        <v>182154000</v>
+        <v>68968000</v>
       </c>
       <c r="AE5" t="n">
         <v>-15000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1121948000</v>
+        <v>-2032969000</v>
       </c>
       <c r="AI5" t="n">
-        <v>34193000</v>
+        <v>105338000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1156141000</v>
+        <v>-2138307000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1039758000</v>
+        <v>-114666000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-409241000</v>
+        <v>-185176000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2830406000</v>
+        <v>-2446048000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3182000</v>
+        <v>3733000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-771435000</v>
+        <v>1975488000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1670971000</v>
+        <v>417580000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1152141000</v>
+        <v>-4742713000</v>
       </c>
       <c r="AR5" t="n">
-        <v>254271000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
+        <v>793421000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>658041000</v>
+        <v>947865000</v>
       </c>
       <c r="AV5" t="n">
-        <v>70996000</v>
+        <v>70307000</v>
       </c>
       <c r="AW5" t="n">
-        <v>587045000</v>
+        <v>877558000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1748599000</v>
+        <v>502632000</v>
       </c>
       <c r="AY5" t="n">
-        <v>58554000</v>
+        <v>-168462000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-5196000</v>
+        <v>-9727000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-201005000</v>
+        <v>2572000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-2052080000</v>
+        <v>-7138421000</v>
       </c>
     </row>
   </sheetData>
@@ -3570,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL2"/>
+  <dimension ref="A1:EJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3716,570 +3771,560 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
       <c r="EH1" t="inlineStr">
         <is>
-          <t>regularMarketTime</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
         <is>
-          <t>shortName</t>
+          <t>longName</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4361,7 +4406,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Changqun  Ji', 'age': 56, 'title': 'Chairman &amp; CEO', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 384503, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chen  Shen', 'age': 53, 'title': 'Financial Controller &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 1425673, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wei  Du', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2024, 'totalPay': 2093920, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jinzhu  Ge', 'age': 39, 'title': 'Executive Director &amp; Assistant to CEO', 'yearBorn': 1986, 'fiscalYear': 2024, 'totalPay': 1333021, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fei  Zhou', 'age': 42, 'title': 'Assistant to Chief Executive Officer', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ying  Seto', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2024, 'totalPay': 8107, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Changqun  Ji', 'age': 56, 'title': 'Chairman &amp; CEO', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 384542, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chen  Shen', 'age': 53, 'title': 'Financial Controller &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 1425817, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wei  Du', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2024, 'totalPay': 2094132, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jinzhu  Ge', 'age': 39, 'title': 'Executive Director &amp; Assistant to CEO', 'yearBorn': 1986, 'fiscalYear': 2024, 'totalPay': 1333156, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fei  Zhou', 'age': 42, 'title': 'Assistant to Chief Executive Officer', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ying  Seto', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2024, 'totalPay': 8108, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4379,415 +4424,409 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>0.89</v>
       </c>
       <c r="X2" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.28</v>
+        <v>0.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2902350</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2902350</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>411948</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>290235</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>290235</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>566719872</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>566719901</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.024924079</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.3702</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.861795</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13226580992</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.20522</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>362955442</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>636763934</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.48284</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>636763934</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>14.127283</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.06299867000000001</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1735603200</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1751241600</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-4666160128</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="BO2" t="n">
+        <v>1701648000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-4.086</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.1190476</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BU2" t="n">
         <v>1527552000</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BY2" t="n">
+        <v>6853415936</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>10.763</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>-3236680960</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>12104066048</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.221</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>22737846272</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>81.434</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>35.708</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>-0.051149998</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>-0.36719</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>3993483008</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-2695739392</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1687207936</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0.17563</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>-0.14235</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.08926000000000001</v>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>0607.HK</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CW2" t="b">
         <v>0</v>
       </c>
-      <c r="AE2" t="n">
-        <v>2.968</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3738500</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3738500</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1006299</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>-35.507248</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>1781769258</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>finmb_271948684</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>FULLSHARE</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AM2" t="n">
+      <c r="DL2" t="n">
+        <v>1040175000000</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0.89 - 1.38</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>411948</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>5.357143</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.14 - 1.95</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-1.0600001</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.5435898</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>111.90476</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1756378740</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1756728000</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.48020005</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.3504598</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.028204978</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.032728173</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>878734208</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>878734228</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>247.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.038646325</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.3708</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.791595</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>13226580992</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.20522</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>362955442</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>636763934</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.48284</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>636763934</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>14.125855</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.09769319999999999</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1735603200</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1751241600</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-4666160128</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-8.49</v>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1701648000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>-4.086</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1527552000</v>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CA2" t="n">
-        <v>6853415936</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>10.763</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>-3236680960</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>12104066048</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.221</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>22737846272</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>81.434</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>35.708</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>-0.051149998</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-0.36719</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>3993483008</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-2695739392</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1687207936</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>-0.038</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.17563</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>-0.14235</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.08926000000000001</v>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0607.HK</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>finmb_271948684</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>9.523809</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.009199977</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.0067113927</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.588405</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.74331576</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1040175000000</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.120000005</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>1.28 - 1.49</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>1006299</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>8.857142</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>0.14 - 1.95</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.57000005</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.2923077</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>200</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1756378740</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1756728000</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-8.49</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>1774943824</v>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>FULLSHARE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
           <t>Fullshare Holdings Limited</t>
         </is>
       </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
